--- a/checklist_forms/027_template_covid_19_daily_health_checklist_city_of_fresno--checklist_forms.xlsx
+++ b/checklist_forms/027_template_covid_19_daily_health_checklist_city_of_fresno--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -937,17 +937,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>covid_symptoms_choices</t>
+          <t>contact_with_covid_positive_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>new_loss_of_taste_or_smell</t>
+          <t>family_member_or_house_hold_member</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New loss of taste or smell</t>
+          <t>Family member or house hold member</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>family_member_or_house_hold_member</t>
+          <t>friend_or_social_friend</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Family member or house hold member</t>
+          <t>Friend or social friend</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>friend_or_social_friend</t>
+          <t>co-worker</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friend or social friend</t>
+          <t>Co-worker</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co-worker</t>
+          <t>classmate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Co-worker</t>
+          <t>Classmate</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>classmate</t>
+          <t>teacher_or_professor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Classmate</t>
+          <t>Teacher or professor</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>teacher_or_professor</t>
+          <t>neighbor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teacher or professor</t>
+          <t>Neighbor</t>
         </is>
       </c>
     </row>
@@ -1044,29 +1044,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>neighbor</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Neighbor</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>contact_with_covid_positive_choices</t>
+          <t>traveled_to_covid_hotspot_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1078,29 +1078,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>traveled_to_covid_hotspot_choices</t>
+          <t>traveled_abroad_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1112,29 +1112,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>traveled_abroad_choices</t>
+          <t>have_you_received_a_vaccination_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1146,27 +1146,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>have_you_received_a_vaccination_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>False</t>
         </is>
